--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>421</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
